--- a/Reports/teachers_grades_shiraz2026.xlsx
+++ b/Reports/teachers_grades_shiraz2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IMC_1\Documents\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E61DA8-D506-4841-B938-0631DAF29E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1483E908-2161-41CD-AB42-3C14C3A56615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{001B96FF-34AA-45A7-A35C-B7BC922ACB0E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Teacher_id</t>
   </si>
@@ -109,6 +109,9 @@
   <si>
     <t>score22</t>
   </si>
+  <si>
+    <t>total</t>
+  </si>
 </sst>
 </file>
 
@@ -168,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -180,6 +183,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -512,16 +516,38 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="3">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{29314932-9508-4441-A0B4-A32B58FE3F54}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;20c55c49-3df4-46a6-94b6-3f8333da6ab7&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7382AA-1F78-4156-8AD8-EAD77507558A}">
-  <dimension ref="A1:W69"/>
+  <dimension ref="A1:X69"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="16.33203125" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -591,8 +617,11 @@
       <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>980755052</v>
       </c>
@@ -662,8 +691,12 @@
       <c r="W2" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X2" s="4">
+        <f>SUM(B2:W2)</f>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>968485078</v>
       </c>
@@ -733,8 +766,12 @@
       <c r="W3" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X3" s="4">
+        <f t="shared" ref="X3:X66" si="0">SUM(B3:W3)</f>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>850091158</v>
       </c>
@@ -804,8 +841,12 @@
       <c r="W4" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X4" s="4">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>938097144</v>
       </c>
@@ -875,8 +916,12 @@
       <c r="W5" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X5" s="4">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>900459736</v>
       </c>
@@ -946,8 +991,12 @@
       <c r="W6" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X6" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>907943997</v>
       </c>
@@ -1017,8 +1066,12 @@
       <c r="W7" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X7" s="4">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>906461728</v>
       </c>
@@ -1088,8 +1141,12 @@
       <c r="W8" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X8" s="4">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>910454214</v>
       </c>
@@ -1159,8 +1216,12 @@
       <c r="W9" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X9" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>913216859</v>
       </c>
@@ -1230,8 +1291,12 @@
       <c r="W10" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X10" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>406359927</v>
       </c>
@@ -1301,8 +1366,12 @@
       <c r="W11" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X11" s="4">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>977865948</v>
       </c>
@@ -1372,8 +1441,12 @@
       <c r="W12" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X12" s="4">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>401825245</v>
       </c>
@@ -1443,8 +1516,12 @@
       <c r="W13" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X13" s="4">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>853276004</v>
       </c>
@@ -1514,8 +1591,12 @@
       <c r="W14" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X14" s="4">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>913202164</v>
       </c>
@@ -1585,8 +1666,12 @@
       <c r="W15" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X15" s="4">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>945665354</v>
       </c>
@@ -1656,8 +1741,12 @@
       <c r="W16" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X16" s="4">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>859709644</v>
       </c>
@@ -1727,8 +1816,12 @@
       <c r="W17" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X17" s="4">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>939383568</v>
       </c>
@@ -1798,8 +1891,12 @@
       <c r="W18" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X18" s="4">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>853040657</v>
       </c>
@@ -1869,8 +1966,12 @@
       <c r="W19" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X19" s="4">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>973110670</v>
       </c>
@@ -1940,8 +2041,12 @@
       <c r="W20" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X20" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>900064205</v>
       </c>
@@ -2011,8 +2116,12 @@
       <c r="W21" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X21" s="4">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>853572311</v>
       </c>
@@ -2082,8 +2191,12 @@
       <c r="W22" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X22" s="4">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>403423981</v>
       </c>
@@ -2153,8 +2266,12 @@
       <c r="W23" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X23" s="4">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>406474395</v>
       </c>
@@ -2224,8 +2341,12 @@
       <c r="W24" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X24" s="4">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>410698427</v>
       </c>
@@ -2295,8 +2416,12 @@
       <c r="W25" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X25" s="4">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>949567580</v>
       </c>
@@ -2366,8 +2491,12 @@
       <c r="W26" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X26" s="4">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>919094060</v>
       </c>
@@ -2437,8 +2566,12 @@
       <c r="W27" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X27" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>902442078</v>
       </c>
@@ -2508,8 +2641,12 @@
       <c r="W28" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X28" s="4">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>907586069</v>
       </c>
@@ -2579,8 +2716,12 @@
       <c r="W29" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X29" s="4">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>907942197</v>
       </c>
@@ -2650,8 +2791,12 @@
       <c r="W30" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X30" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>902389196</v>
       </c>
@@ -2721,8 +2866,12 @@
       <c r="W31" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X31" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>941512303</v>
       </c>
@@ -2792,8 +2941,12 @@
       <c r="W32" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X32" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>850202847</v>
       </c>
@@ -2863,8 +3016,12 @@
       <c r="W33" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X33" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>904969409</v>
       </c>
@@ -2934,8 +3091,12 @@
       <c r="W34" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X34" s="4">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>911686699</v>
       </c>
@@ -3005,8 +3166,12 @@
       <c r="W35" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X35" s="4">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>984961466</v>
       </c>
@@ -3076,8 +3241,12 @@
       <c r="W36" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X36" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>852302116</v>
       </c>
@@ -3147,8 +3316,12 @@
       <c r="W37" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X37" s="4">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>904994597</v>
       </c>
@@ -3218,8 +3391,12 @@
       <c r="W38" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X38" s="4">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>900122409</v>
       </c>
@@ -3289,8 +3466,12 @@
       <c r="W39" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X39" s="4">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>953107901</v>
       </c>
@@ -3360,8 +3541,12 @@
       <c r="W40" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X40" s="4">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>403826068</v>
       </c>
@@ -3431,8 +3616,12 @@
       <c r="W41" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X41" s="4">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>989552252</v>
       </c>
@@ -3502,8 +3691,12 @@
       <c r="W42" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X42" s="4">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>852192368</v>
       </c>
@@ -3573,8 +3766,12 @@
       <c r="W43" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X43" s="4">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>911683332</v>
       </c>
@@ -3644,8 +3841,12 @@
       <c r="W44" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X44" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>858970445</v>
       </c>
@@ -3715,8 +3916,12 @@
       <c r="W45" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X45" s="4">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>994329175</v>
       </c>
@@ -3786,8 +3991,12 @@
       <c r="W46" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X46" s="4">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>954240850</v>
       </c>
@@ -3857,8 +4066,12 @@
       <c r="W47" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X47" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>401555594</v>
       </c>
@@ -3928,8 +4141,12 @@
       <c r="W48" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X48" s="4">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>907952691</v>
       </c>
@@ -3999,8 +4216,12 @@
       <c r="W49" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X49" s="4">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>402189757</v>
       </c>
@@ -4070,8 +4291,12 @@
       <c r="W50" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X50" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>912621182</v>
       </c>
@@ -4141,8 +4366,12 @@
       <c r="W51" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X51" s="4">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>997950167</v>
       </c>
@@ -4212,8 +4441,12 @@
       <c r="W52" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X52" s="4">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>851544346</v>
       </c>
@@ -4283,8 +4516,12 @@
       <c r="W53" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X53" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>851723775</v>
       </c>
@@ -4354,8 +4591,12 @@
       <c r="W54" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X54" s="4">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>853977841</v>
       </c>
@@ -4425,8 +4666,12 @@
       <c r="W55" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X55" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>401012653</v>
       </c>
@@ -4496,8 +4741,12 @@
       <c r="W56" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X56" s="4">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>854879103</v>
       </c>
@@ -4567,8 +4816,12 @@
       <c r="W57" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X57" s="4">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>850379611</v>
       </c>
@@ -4638,8 +4891,12 @@
       <c r="W58" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X58" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>927702787</v>
       </c>
@@ -4709,8 +4966,12 @@
       <c r="W59" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X59" s="4">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>906832084</v>
       </c>
@@ -4780,8 +5041,12 @@
       <c r="W60" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X60" s="4">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>946826138</v>
       </c>
@@ -4851,8 +5116,12 @@
       <c r="W61" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X61" s="4">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>854136140</v>
       </c>
@@ -4922,8 +5191,12 @@
       <c r="W62" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X62" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>939380949</v>
       </c>
@@ -4993,8 +5266,12 @@
       <c r="W63" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X63" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>853214500</v>
       </c>
@@ -5064,8 +5341,12 @@
       <c r="W64" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X64" s="4">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>984961474</v>
       </c>
@@ -5135,8 +5416,12 @@
       <c r="W65" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X65" s="4">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>858609795</v>
       </c>
@@ -5206,8 +5491,12 @@
       <c r="W66" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X66" s="4">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>936853365</v>
       </c>
@@ -5277,8 +5566,12 @@
       <c r="W67" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X67" s="4">
+        <f t="shared" ref="X67:X69" si="1">SUM(B67:W67)</f>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>403420359</v>
       </c>
@@ -5348,8 +5641,12 @@
       <c r="W68" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X68" s="4">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>401485187</v>
       </c>
@@ -5418,6 +5715,10 @@
       </c>
       <c r="W69" s="1">
         <v>2</v>
+      </c>
+      <c r="X69" s="4">
+        <f t="shared" si="1"/>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
